--- a/dist/checklists/xlsx/rembi/rembi_image_manifest_v0.1.xlsx
+++ b/dist/checklists/xlsx/rembi/rembi_image_manifest_v0.1.xlsx
@@ -1167,7 +1167,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="B6EE" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C5BF" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5314,7 +5314,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AAF1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="AFF1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -11416,7 +11416,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A0E4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FCC0" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -16518,7 +16518,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DDE1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="ACA8" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -21598,7 +21598,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AD79" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="848A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -26700,7 +26700,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C76F" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D211" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -32825,7 +32825,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F0B8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8E38" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -32955,7 +32955,7 @@
       <c r="I4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="9A22" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FD72" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -36036,7 +36036,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="8384" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="88DC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:C4"/>
   </mergeCells>
@@ -39136,7 +39136,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="BBD8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D459" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -42214,7 +42214,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="919F" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EBEC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -46293,7 +46293,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A96A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="9072" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -50427,7 +50427,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C30D" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="BB37" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -55567,7 +55567,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="B1EB" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EC7C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/rembi/rembi_image_manifest_v0.1.xlsx
+++ b/dist/checklists/xlsx/rembi/rembi_image_manifest_v0.1.xlsx
@@ -1167,7 +1167,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="C5BF" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EF20" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5314,7 +5314,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="AFF1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DD7A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -11416,7 +11416,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="FCC0" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F16E" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -16518,7 +16518,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="ACA8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C82D" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -21598,7 +21598,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="848A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EBB7" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -26700,7 +26700,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="D211" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FBAA" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -32825,7 +32825,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="8E38" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C957" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -32955,7 +32955,7 @@
       <c r="I4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="FD72" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8753" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -36036,7 +36036,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="88DC" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F4F7" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:C4"/>
   </mergeCells>
@@ -39136,7 +39136,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="D459" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A7EC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -42214,7 +42214,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EBEC" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E96C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -46293,7 +46293,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="9072" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DCE0" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -50427,7 +50427,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="BB37" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C4A9" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -55567,7 +55567,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8736" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/rembi/rembi_image_manifest_v0.1.xlsx
+++ b/dist/checklists/xlsx/rembi/rembi_image_manifest_v0.1.xlsx
@@ -1167,7 +1167,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EF20" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D71E" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5314,7 +5314,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DD7A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="AF4C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:K4"/>
   </mergeCells>
@@ -11416,7 +11416,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F16E" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="FC2A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -16518,7 +16518,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C82D" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="DDF1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -21598,7 +21598,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EBB7" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D477" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -26700,7 +26700,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="FBAA" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C905" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -32825,7 +32825,7 @@
       <c r="D1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C957" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A7DD" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -32955,7 +32955,7 @@
       <c r="I4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="8753" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E18C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -36036,7 +36036,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="F4F7" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8535" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:C4"/>
   </mergeCells>
@@ -39136,7 +39136,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="A7EC" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EC33" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:F4"/>
   </mergeCells>
@@ -42214,7 +42214,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="E96C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D53B" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -46293,7 +46293,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="DCE0" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EC19" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -50427,7 +50427,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C4A9" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="EAE2" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -55567,7 +55567,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="8736" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="932A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:I4"/>
   </mergeCells>
